--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76272086</v>
+        <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>111175</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,41 +912,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Porskärr N, Öl</t>
+          <t>Porskärr, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592785</v>
+        <v>592769</v>
       </c>
       <c r="R4" t="n">
-        <v>6284018</v>
+        <v>6283980</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-03-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-03-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,29 +989,1781 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137140981</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137140982</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592679</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6284008</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137140982</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>76272086</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Porskärr N, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592785</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6284018</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Jan-Olof Petersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Jan-Olof Petersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/76272086</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137141642</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111452</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592861</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6283957</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141642</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137141640</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99704</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219878</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Storrams</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygonatum multiflorum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592801</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6283968</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141640</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137141619</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592754</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6284041</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141619</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137141620</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592739</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6284044</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141620</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137141621</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592731</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6284042</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141621</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137141622</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592704</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6284036</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141622</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137141623</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592719</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6283964</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141623</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137141626</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>592843</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6283969</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141626</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137141628</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107079</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>592838</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6283961</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141628</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137141630</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100134</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592786</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6283953</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141630</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137141633</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100134</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592767</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6284000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141633</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137141635</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100134</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592746</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6284004</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141635</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137141638</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100134</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592758</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6284007</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141638</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137141639</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104891</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592798</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6283975</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141639</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137141618</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101578</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Porskärr, Öl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>592746</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6284009</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Algutsrum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137141618</t>
         </is>
       </c>
     </row>
@@ -1015,6 +2772,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111452</v>
+        <v>111456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99704</v>
+        <v>99708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100134</v>
+        <v>100138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100134</v>
+        <v>100138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100134</v>
+        <v>100138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100134</v>
+        <v>100138</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111456</v>
+        <v>111458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99708</v>
+        <v>99710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100138</v>
+        <v>100140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100138</v>
+        <v>100140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100138</v>
+        <v>100140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100138</v>
+        <v>100140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111458</v>
+        <v>111460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99710</v>
+        <v>99712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100140</v>
+        <v>100142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100140</v>
+        <v>100142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100140</v>
+        <v>100142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100140</v>
+        <v>100142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137140982</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111460</v>
+        <v>111473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99712</v>
+        <v>99725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100142</v>
+        <v>100155</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100142</v>
+        <v>100155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100142</v>
+        <v>100155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100142</v>
+        <v>100155</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>137140982</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57960</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111473</v>
+        <v>111475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99725</v>
+        <v>99727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100155</v>
+        <v>100157</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100155</v>
+        <v>100157</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100155</v>
+        <v>100157</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100155</v>
+        <v>100157</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -934,11 +934,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Porskärr, Öl</t>
@@ -1045,16 +1041,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Porskärr, Öl</t>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111475</v>
+        <v>111481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99727</v>
+        <v>99730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100157</v>
+        <v>100160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100157</v>
+        <v>100160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100157</v>
+        <v>100160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100157</v>
+        <v>100160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>137140982</v>
       </c>
       <c r="B5" t="n">
-        <v>57960</v>
+        <v>57970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111481</v>
+        <v>111503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99730</v>
+        <v>99740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100160</v>
+        <v>100170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100160</v>
+        <v>100170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100160</v>
+        <v>100170</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100160</v>
+        <v>100170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111503</v>
+        <v>111504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99740</v>
+        <v>99741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100170</v>
+        <v>100171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100170</v>
+        <v>100171</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100170</v>
+        <v>100171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100170</v>
+        <v>100171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>137140982</v>
       </c>
       <c r="B5" t="n">
-        <v>57970</v>
+        <v>57971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111504</v>
+        <v>111509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99741</v>
+        <v>99746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100171</v>
+        <v>100176</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100171</v>
+        <v>100176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100171</v>
+        <v>100176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100171</v>
+        <v>100176</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111509</v>
+        <v>111512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99746</v>
+        <v>99749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100176</v>
+        <v>100179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100176</v>
+        <v>100179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100176</v>
+        <v>100179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100176</v>
+        <v>100179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>137140982</v>
       </c>
       <c r="B5" t="n">
-        <v>57971</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111512</v>
+        <v>111518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99749</v>
+        <v>99755</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100179</v>
+        <v>100185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100179</v>
+        <v>100185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100179</v>
+        <v>100185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100179</v>
+        <v>100185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111518</v>
+        <v>111519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111519</v>
+        <v>111531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99755</v>
+        <v>99767</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100185</v>
+        <v>100197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100185</v>
+        <v>100197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100185</v>
+        <v>100197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100185</v>
+        <v>100197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111531</v>
+        <v>111532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99767</v>
+        <v>99768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100197</v>
+        <v>100198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100197</v>
+        <v>100198</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100197</v>
+        <v>100198</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100197</v>
+        <v>100198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111532</v>
+        <v>111535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99768</v>
+        <v>99771</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100198</v>
+        <v>100201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100198</v>
+        <v>100201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100198</v>
+        <v>100201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100198</v>
+        <v>100201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 15600-2025 artfynd.xlsx
+++ b/artfynd/A 15600-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>137140981</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>137140982</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137141642</v>
       </c>
       <c r="B7" t="n">
-        <v>111535</v>
+        <v>111541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>137141640</v>
       </c>
       <c r="B8" t="n">
-        <v>99771</v>
+        <v>99775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>137141619</v>
       </c>
       <c r="B9" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>137141620</v>
       </c>
       <c r="B10" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>137141621</v>
       </c>
       <c r="B11" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>137141622</v>
       </c>
       <c r="B12" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>137141623</v>
       </c>
       <c r="B13" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>137141626</v>
       </c>
       <c r="B14" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>137141628</v>
       </c>
       <c r="B15" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137141630</v>
       </c>
       <c r="B16" t="n">
-        <v>100201</v>
+        <v>100205</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137141633</v>
       </c>
       <c r="B17" t="n">
-        <v>100201</v>
+        <v>100205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137141635</v>
       </c>
       <c r="B18" t="n">
-        <v>100201</v>
+        <v>100205</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137141638</v>
       </c>
       <c r="B19" t="n">
-        <v>100201</v>
+        <v>100205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>137141639</v>
       </c>
       <c r="B20" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137141618</v>
       </c>
       <c r="B21" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
